--- a/output/mobility_report_summary.xlsx
+++ b/output/mobility_report_summary.xlsx
@@ -443,13 +443,13 @@
         <v>2022</v>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="C2" t="n">
         <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="3">
@@ -457,13 +457,13 @@
         <v>2023</v>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="C3" t="n">
         <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="4">
@@ -471,13 +471,13 @@
         <v>2024</v>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="C4" t="n">
         <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="5">
@@ -485,13 +485,13 @@
         <v>2025</v>
       </c>
       <c r="B5" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="C5" t="n">
         <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="6">
@@ -499,13 +499,13 @@
         <v>2026</v>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="C6" t="n">
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
